--- a/ig/DM-JUIN-2025/ASS-X11-FinessAgregatStatutJuridique.xlsx
+++ b/ig/DM-JUIN-2025/ASS-X11-FinessAgregatStatutJuridique.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-23T14:52:27+00:00</t>
+    <t>2025-06-25T14:46:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUIN-2025/ASS-X11-FinessAgregatStatutJuridique.xlsx
+++ b/ig/DM-JUIN-2025/ASS-X11-FinessAgregatStatutJuridique.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-25T14:46:29+00:00</t>
+    <t>2025-06-25T15:44:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUIN-2025/ASS-X11-FinessAgregatStatutJuridique.xlsx
+++ b/ig/DM-JUIN-2025/ASS-X11-FinessAgregatStatutJuridique.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-25T15:44:51+00:00</t>
+    <t>2025-06-25T16:27:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUIN-2025/ASS-X11-FinessAgregatStatutJuridique.xlsx
+++ b/ig/DM-JUIN-2025/ASS-X11-FinessAgregatStatutJuridique.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-25T16:27:19+00:00</t>
+    <t>2025-06-26T12:59:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUIN-2025/ASS-X11-FinessAgregatStatutJuridique.xlsx
+++ b/ig/DM-JUIN-2025/ASS-X11-FinessAgregatStatutJuridique.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-26T12:59:08+00:00</t>
+    <t>2025-06-27T11:29:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUIN-2025/ASS-X11-FinessAgregatStatutJuridique.xlsx
+++ b/ig/DM-JUIN-2025/ASS-X11-FinessAgregatStatutJuridique.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-27T11:29:56+00:00</t>
+    <t>2025-06-27T14:01:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUIN-2025/ASS-X11-FinessAgregatStatutJuridique.xlsx
+++ b/ig/DM-JUIN-2025/ASS-X11-FinessAgregatStatutJuridique.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-27T14:01:20+00:00</t>
+    <t>2025-06-30T13:02:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-JUIN-2025/ASS-X11-FinessAgregatStatutJuridique.xlsx
+++ b/ig/DM-JUIN-2025/ASS-X11-FinessAgregatStatutJuridique.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-30T13:02:18+00:00</t>
+    <t>2025-06-30T14:19:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
